--- a/artfynd/A 52808-2022 artfynd.xlsx
+++ b/artfynd/A 52808-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 52808-2022 artfynd.xlsx
+++ b/artfynd/A 52808-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1136,6 +1136,131 @@
           <t>Länsstyrelsen i Uppsala län, områdesskydd</t>
         </is>
       </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>124215923</v>
+      </c>
+      <c r="B6" t="n">
+        <v>103506</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="N6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Norrängarna, Upl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>679965</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6685240</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Uppsala</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Östhammar</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Uppland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Hökhuvud</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-04-18</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>16:00</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF6" t="inlineStr"/>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Susanne Åkesson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Susanne Åkesson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 52808-2022 artfynd.xlsx
+++ b/artfynd/A 52808-2022 artfynd.xlsx
@@ -1388,10 +1388,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124250523</v>
+        <v>124260637</v>
       </c>
       <c r="B8" t="n">
-        <v>96979</v>
+        <v>98124</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1404,50 +1404,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>221945</v>
+        <v>219847</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ånö, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>680129</v>
+        <v>679995</v>
       </c>
       <c r="R8" t="n">
-        <v>6685027</v>
+        <v>6685188</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1477,14 +1473,19 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Stor samling av plantor över minst 20 kvm.</t>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1512,10 +1513,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124260637</v>
+        <v>124250523</v>
       </c>
       <c r="B9" t="n">
-        <v>98124</v>
+        <v>96979</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1528,46 +1529,50 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>219847</v>
+        <v>221945</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ånö, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>679995</v>
+        <v>680129</v>
       </c>
       <c r="R9" t="n">
-        <v>6685188</v>
+        <v>6685027</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1597,19 +1602,14 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>16:30</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Stor samling av plantor över minst 20 kvm.</t>
         </is>
       </c>
       <c r="AD9" t="b">

--- a/artfynd/A 52808-2022 artfynd.xlsx
+++ b/artfynd/A 52808-2022 artfynd.xlsx
@@ -1388,10 +1388,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>124260637</v>
+        <v>124250523</v>
       </c>
       <c r="B8" t="n">
-        <v>98124</v>
+        <v>96979</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1404,46 +1404,50 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219847</v>
+        <v>221945</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>20</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Ånö, Upl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>679995</v>
+        <v>680129</v>
       </c>
       <c r="R8" t="n">
-        <v>6685188</v>
+        <v>6685027</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1473,19 +1477,14 @@
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>16:30</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>16:30</t>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Stor samling av plantor över minst 20 kvm.</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1513,10 +1512,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>124250523</v>
+        <v>124260637</v>
       </c>
       <c r="B9" t="n">
-        <v>96979</v>
+        <v>98124</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1529,50 +1528,46 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221945</v>
+        <v>219847</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr"/>
-      <c r="N9" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
           <t>Ånö, Upl</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>680129</v>
+        <v>679995</v>
       </c>
       <c r="R9" t="n">
-        <v>6685027</v>
+        <v>6685188</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1602,14 +1597,19 @@
           <t>2025-04-18</t>
         </is>
       </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>16:30</t>
+        </is>
+      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-04-18</t>
         </is>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>Stor samling av plantor över minst 20 kvm.</t>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>16:30</t>
         </is>
       </c>
       <c r="AD9" t="b">
